--- a/output/pdf_financials_xlsx/RE.xlsx
+++ b/output/pdf_financials_xlsx/RE.xlsx
@@ -4062,22 +4062,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.115565</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.613801</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.632219</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.871649</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.73176</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.242181</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -6845,7 +6845,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -8255,7 +8259,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -9634,7 +9642,11 @@
           <t>Reserves 12 (c)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.115565</v>
       </c>
@@ -10238,7 +10250,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -27596,10 +27612,10 @@
         </is>
       </c>
       <c r="E365" s="5" t="n">
-        <v>0.009468000000000001</v>
+        <v>-0.009468000000000001</v>
       </c>
       <c r="F365" s="5" t="n">
-        <v>0.043349</v>
+        <v>-0.043349</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RE.xlsx
+++ b/output/pdf_financials_xlsx/RE.xlsx
@@ -9945,7 +9945,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">

--- a/output/pdf_financials_xlsx/RE.xlsx
+++ b/output/pdf_financials_xlsx/RE.xlsx
@@ -1523,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.012981</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.019478</v>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         <v>-1.636047</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.041402</v>
+        <v>-3.028421</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.80289</v>
+        <v>-3.783412</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>-78.42482793531001</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-186.2052456286428</v>
+        <v>-185.4105035019836</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-97.71613092541625</v>
+        <v>-97.21563924720172</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.012981</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.019478</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -10844,7 +10844,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RE.xlsx
+++ b/output/pdf_financials_xlsx/RE.xlsx
@@ -11322,7 +11322,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
